--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/updateWithExercises-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/updateWithExercises-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="90">
   <si>
     <t>Statement: WorkoutSessionRepository.updateWithExercises(id, data, exercises) – atomically replaces metadata and exercises.</t>
   </si>
@@ -133,10 +133,67 @@
     <t>Passed</t>
   </si>
   <si>
+    <t>Number BVA</t>
+  </si>
+  <si>
+    <t>BVA Test Case</t>
+  </si>
+  <si>
+    <t>ID length</t>
+  </si>
+  <si>
+    <t>id = ""</t>
+  </si>
+  <si>
+    <t>id = "a" (inex)</t>
+  </si>
+  <si>
+    <t>id = "a" (exist)</t>
+  </si>
+  <si>
+    <t>Exercises length</t>
+  </si>
+  <si>
+    <t>length = 1</t>
+  </si>
+  <si>
+    <t>BVA</t>
+  </si>
+  <si>
+    <t>BVA-1 EmptyID</t>
+  </si>
+  <si>
+    <t>Throws NotFoundError</t>
+  </si>
+  <si>
+    <t>BVA-2 InexCharID</t>
+  </si>
+  <si>
+    <t>BVA-3 ExistCharID</t>
+  </si>
+  <si>
+    <t>Updates successfully</t>
+  </si>
+  <si>
+    <t>TC from EC</t>
+  </si>
+  <si>
+    <t>TC from BVA</t>
+  </si>
+  <si>
+    <t>EC-1, EC-4</t>
+  </si>
+  <si>
+    <t>Existing session, valid update</t>
+  </si>
+  <si>
+    <t>Returns session</t>
+  </si>
+  <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>Exercises=[]</t>
+    <t>Exercises array empty</t>
   </si>
   <si>
     <t>Throws error</t>
@@ -145,124 +202,49 @@
     <t>EC-5</t>
   </si>
   <si>
-    <t>Non-existent session</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
+    <t>Non-existent session ID</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>Kept item included</t>
-  </si>
-  <si>
-    <t>Updated in place</t>
+    <t>Include existing exercise ID</t>
+  </si>
+  <si>
+    <t>Updates in place</t>
   </si>
   <si>
     <t>EC-7</t>
   </si>
   <si>
-    <t>Stale item omitted</t>
-  </si>
-  <si>
-    <t>Deleted from DB</t>
+    <t>Omit current exercise ID</t>
+  </si>
+  <si>
+    <t>Exercise row is deleted</t>
+  </si>
+  <si>
+    <t>EC-8</t>
+  </si>
+  <si>
+    <t>Correct operations</t>
   </si>
   <si>
     <t>EC-10</t>
   </si>
   <si>
-    <t>DB failure</t>
+    <t>Database write error</t>
   </si>
   <si>
     <t>Throws TransactionError</t>
   </si>
   <si>
-    <t>Number BVA</t>
-  </si>
-  <si>
-    <t>BVA Test Case</t>
-  </si>
-  <si>
-    <t>ID length</t>
-  </si>
-  <si>
-    <t>id = ""</t>
-  </si>
-  <si>
-    <t>id = "a"</t>
-  </si>
-  <si>
-    <t>Exercises length</t>
-  </si>
-  <si>
-    <t>length = 1</t>
-  </si>
-  <si>
-    <t>BVA</t>
-  </si>
-  <si>
-    <t>BVA-1 EmptyID</t>
-  </si>
-  <si>
-    <t>BVA-2 OneCharID</t>
-  </si>
-  <si>
-    <t>BVA-3 OneLen</t>
-  </si>
-  <si>
-    <t>Updates successfully</t>
-  </si>
-  <si>
-    <t>TC from EC</t>
-  </si>
-  <si>
-    <t>TC from BVA</t>
-  </si>
-  <si>
-    <t>EC-1, EC-4</t>
-  </si>
-  <si>
-    <t>Existing session, valid update</t>
-  </si>
-  <si>
-    <t>Returns session</t>
-  </si>
-  <si>
-    <t>Exercises array empty</t>
-  </si>
-  <si>
-    <t>Non-existent session ID</t>
-  </si>
-  <si>
-    <t>Include existing exercise ID</t>
-  </si>
-  <si>
-    <t>Updates in place</t>
-  </si>
-  <si>
-    <t>Omit current exercise ID</t>
-  </si>
-  <si>
-    <t>Exercise row is deleted</t>
-  </si>
-  <si>
-    <t>EC-8</t>
-  </si>
-  <si>
-    <t>Mixed: kept, new, and stale items</t>
-  </si>
-  <si>
-    <t>Correct row operations</t>
-  </si>
-  <si>
-    <t>Database write error</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
     <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
   </si>
   <si>
     <t>Testing</t>
@@ -990,7 +972,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1034,91 +1016,6 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1127,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1137,13 +1034,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1151,10 +1048,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1165,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1173,10 +1070,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>59</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1202,7 +1110,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>31</v>
@@ -1219,13 +1127,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>37</v>
@@ -1236,13 +1144,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>37</v>
@@ -1253,13 +1161,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>37</v>
@@ -1273,7 +1181,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1289,10 +1197,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>31</v>
@@ -1309,16 +1217,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>37</v>
@@ -1329,16 +1237,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>37</v>
@@ -1349,16 +1257,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>37</v>
@@ -1369,16 +1277,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>37</v>
@@ -1389,16 +1297,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>37</v>
@@ -1409,16 +1317,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>37</v>
@@ -1429,16 +1337,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>37</v>
@@ -1452,13 +1360,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>37</v>
@@ -1472,15 +1380,35 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="E11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1509,16 +1437,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1526,45 +1454,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B3" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1573,19 +1501,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/updateWithExercises-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/updateWithExercises-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="90">
-  <si>
-    <t>Statement: WorkoutSessionRepository.updateWithExercises(id, data, exercises) – atomically replaces metadata and exercises.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="89">
+  <si>
+    <t>Statement: WorkoutSessionRepository.updateWithExercises(id, data, exercises) – Atomically updates a workout session's metadata and replaces its exercises. New exercises (no id) are created; existing exercises (with id) are updated; exercises omitted from the input are deleted. Returns the updated WorkoutSessionWithExercises on success. Throws WorkoutSessionRequiresExercisesError("A workout session must include at least one exercise.") if the exercises array is empty. Throws NotFoundError("Workout session not found") if no session exists with the given ID. Throws TransactionError if the transaction fails.</t>
   </si>
   <si>
     <t/>
@@ -37,19 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible | exercises.length &gt;= 1</t>
+    <t>Database is accessible. A workout session with the given ID may or may not exist. The exercises array may be empty or contain new items (no id), existing items (with id), or a mix of both.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;WorkoutSessionWithExercises&gt; | throws Error</t>
+    <t>Output: Promise&lt;WorkoutSessionWithExercises&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Atomically updates all or nothing.</t>
+    <t>On success: WorkoutSessionWithExercises returned with result.id matching input id, result.exercises reflecting the provided exercises after create/update/delete reconciliation. On failure: WorkoutSessionRequiresExercisesError, NotFoundError, or TransactionError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,46 +64,43 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>Exercises list</t>
-  </si>
-  <si>
-    <t>Length &gt;= 1</t>
-  </si>
-  <si>
-    <t>Multiple exercises</t>
-  </si>
-  <si>
-    <t>Length = 0 (RequiresExercisesError)</t>
-  </si>
-  <si>
     <t>Session existence</t>
   </si>
   <si>
-    <t>Found</t>
-  </si>
-  <si>
-    <t>Not found (NotFoundError)</t>
-  </si>
-  <si>
-    <t>Exercises state</t>
-  </si>
-  <si>
-    <t>Kept items</t>
-  </si>
-  <si>
-    <t>Stale items removed</t>
-  </si>
-  <si>
-    <t>Mixed items</t>
-  </si>
-  <si>
-    <t>Database status</t>
-  </si>
-  <si>
-    <t>Success</t>
-  </si>
-  <si>
-    <t>Failure (TransactionError)</t>
+    <t>Existing ID, new exercises → WorkoutSessionWithExercises returned with result.id: SESSION_ID, result.exercises.length: 1</t>
+  </si>
+  <si>
+    <t>Non-existent ID → NotFoundError("Workout session not found")</t>
+  </si>
+  <si>
+    <t>Exercise count</t>
+  </si>
+  <si>
+    <t>New exercises provided (no id) → exercises created, result.exercises.length: 1</t>
+  </si>
+  <si>
+    <t>Empty exercises array → WorkoutSessionRequiresExercisesError("A workout session must include at least one exercise.")</t>
+  </si>
+  <si>
+    <t>Exercise mutation</t>
+  </si>
+  <si>
+    <t>Exercise with existing id provided → exercise updated in place, result.exercises[0].sets: 4</t>
+  </si>
+  <si>
+    <t>Exercise omitted from input (stale) → exercise deleted, result equal to MOCK_SESSION_WITH_EXERCISES</t>
+  </si>
+  <si>
+    <t>Mix of existing id (updated) and new (created), stale removed → result.id: SESSION_ID, result equal to MOCK_SESSION_WITH_EXERCISES</t>
+  </si>
+  <si>
+    <t>Transaction</t>
+  </si>
+  <si>
+    <t>Transaction succeeds → WorkoutSessionWithExercises returned</t>
+  </si>
+  <si>
+    <t>Transaction fails → TransactionError("DB connection lost")</t>
   </si>
   <si>
     <t>No TC</t>
@@ -121,18 +118,69 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>EC-1, EC-4, EC-9</t>
-  </si>
-  <si>
-    <t>Exists, valid data, 1 exercise</t>
-  </si>
-  <si>
-    <t>Returns updated session</t>
+    <t>EC-1, EC-3</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT (session exists, new exercises, transaction succeeds)</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with result.id: SESSION_ID, result.exercises.length: 1, result equal to MOCK_SESSION_WITH_EXERCISES</t>
   </si>
   <si>
     <t>Passed</t>
   </si>
   <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, data: UPDATE_SESSION_INPUT, exercises: [] (empty array)</t>
+  </si>
+  <si>
+    <t>throws WorkoutSessionRequiresExercisesError("A workout session must include at least one exercise.")</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>id: NONEXISTENT_ID, data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT (no session with that ID)</t>
+  </si>
+  <si>
+    <t>throws NotFoundError("Workout session not found")</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, data: UPDATE_SESSION_INPUT, exercises: [{ id: "se-uuid-001", exerciseId: EXERCISE_ID, sets: 4, reps: 8, weight: 90.0 }] (session exists, exercise se-uuid-001 exists)</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with result.id: SESSION_ID, result.exercises.length: 1, result.exercises[0].sets: 4</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, data: UPDATE_SESSION_INPUT, exercises: [{ exerciseId: EXERCISE_ID, sets: 5, reps: 5, weight: 100.0 }] (session exists, stale exercise se-uuid-001 removed)</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with result.id: SESSION_ID, result equal to MOCK_SESSION_WITH_EXERCISES</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, data: UPDATE_SESSION_INPUT, exercises: [{ id: "se-uuid-001", ... }, { exerciseId: "exercise-uuid-002", ... }] (session exists, se-uuid-002 stale and removed)</t>
+  </si>
+  <si>
+    <t>EC-9</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT (session exists, transaction fails with "DB connection lost")</t>
+  </si>
+  <si>
+    <t>throws TransactionError("DB connection lost")</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
@@ -142,37 +190,46 @@
     <t>ID length</t>
   </si>
   <si>
-    <t>id = ""</t>
-  </si>
-  <si>
-    <t>id = "a" (inex)</t>
-  </si>
-  <si>
-    <t>id = "a" (exist)</t>
-  </si>
-  <si>
-    <t>Exercises length</t>
-  </si>
-  <si>
-    <t>length = 1</t>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
+  </si>
+  <si>
+    <t>exercises length</t>
+  </si>
+  <si>
+    <t>length: 1 (one new exercise)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 EmptyID</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
-  </si>
-  <si>
-    <t>BVA-2 InexCharID</t>
-  </si>
-  <si>
-    <t>BVA-3 ExistCharID</t>
-  </si>
-  <si>
-    <t>Updates successfully</t>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: "" (no session with that ID), data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT</t>
+  </si>
+  <si>
+    <t>throws NotFoundError</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no session with that ID), data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT</t>
+  </si>
+  <si>
+    <t>id: "a" (session exists with id: "a"), data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with result.id: "a"</t>
+  </si>
+  <si>
+    <t>BVA-2 (l=1)</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, data: UPDATE_SESSION_INPUT, exercises: [{ exerciseId: EXERCISE_ID, sets: 3, reps: 10, weight: 80.0 }] (session exists)</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with result.exercises.length: 1, result.exercises[0].exerciseId: EXERCISE_ID</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -181,72 +238,12 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EC-1, EC-4</t>
-  </si>
-  <si>
-    <t>Existing session, valid update</t>
-  </si>
-  <si>
-    <t>Returns session</t>
-  </si>
-  <si>
-    <t>EC-3</t>
-  </si>
-  <si>
-    <t>Exercises array empty</t>
-  </si>
-  <si>
-    <t>Throws error</t>
-  </si>
-  <si>
-    <t>EC-5</t>
-  </si>
-  <si>
-    <t>Non-existent session ID</t>
-  </si>
-  <si>
-    <t>EC-6</t>
-  </si>
-  <si>
-    <t>Include existing exercise ID</t>
-  </si>
-  <si>
-    <t>Updates in place</t>
-  </si>
-  <si>
-    <t>EC-7</t>
-  </si>
-  <si>
-    <t>Omit current exercise ID</t>
-  </si>
-  <si>
-    <t>Exercise row is deleted</t>
-  </si>
-  <si>
-    <t>EC-8</t>
-  </si>
-  <si>
-    <t>Correct operations</t>
-  </si>
-  <si>
-    <t>EC-10</t>
-  </si>
-  <si>
-    <t>Database write error</t>
-  </si>
-  <si>
-    <t>Throws TransactionError</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>BVA-3</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -277,7 +274,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-06/WSM-07</t>
+    <t>REPO-23</t>
   </si>
   <si>
     <t>n/a</t>
@@ -802,7 +799,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -843,13 +840,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -857,13 +854,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -871,13 +868,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -885,13 +882,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -899,7 +896,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>23</v>
@@ -913,7 +910,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>24</v>
@@ -927,10 +924,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>1</v>
@@ -941,27 +938,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -972,7 +955,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -984,19 +967,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1004,16 +987,118 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E2" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1024,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1034,13 +1119,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1048,10 +1133,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1059,32 +1144,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1095,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1107,19 +1170,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1127,16 +1190,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1144,16 +1207,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1161,16 +1224,33 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1194,22 +1274,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1217,19 +1297,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1237,19 +1317,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1257,19 +1337,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1277,19 +1357,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1297,19 +1377,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1317,19 +1397,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1337,19 +1417,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1363,13 +1443,13 @@
         <v>73</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1380,16 +1460,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1400,16 +1480,36 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1437,16 +1537,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1454,45 +1554,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1501,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
